--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>43555</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44391</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>44425</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44522</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44866</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44967</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>44977</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>44993</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45020</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45039</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45061</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45091</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45204</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45229</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45251</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45258</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45294</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45301</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>43318</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>43336</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>43364</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>43388</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>43391</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43404</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43410</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43413</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43416</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>43425</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43426</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>43431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43434</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43436</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43437</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>43439</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>43441</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>43447</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>43448</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>43450</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>43452</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43454</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>43461</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43462</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43464</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>43471</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>43478</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>43486</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>43487</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>43490</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>43493</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>43498</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>43502</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>43507</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>43508</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>43509</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>43511</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>43522</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>43530</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>43553</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43558</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>43566</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43598</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>43646</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43654</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>43657</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>43669</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>43682</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>43685</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>43689</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>43705</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43707</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43710</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43714</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43716</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43724</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43733</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43747</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43749</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43765</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>43767</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43776</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>43780</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>43782</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>43794</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43808</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43810</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>43811</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>43815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43829</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43837</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43844</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43849</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43850</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43856</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43864</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43866</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43871</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>43873</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>43881</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43892</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>43902</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43912</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43917</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>43933</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>43938</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>43951</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43964</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43973</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43978</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43984</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>43985</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>43986</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>43987</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>43997</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44000</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44002</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44005</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44013</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44049</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44056</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44071</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44073</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44078</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44085</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44088</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44090</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44091</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44096</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44104</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44153</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>44154</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44159</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44161</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44167</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44168</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44172</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44174</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44179</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44181</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44183</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44203</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44207</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44213</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44249</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44274</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44292</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44299</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44305</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44307</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44312</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44319</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44323</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>44326</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44327</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44328</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44335</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44336</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44337</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44349</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44350</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44351</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44371</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44374</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44375</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44376</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44383</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44390</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44393</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44394</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44397</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44399</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44405</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44409</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44413</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>44420</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>44431</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44432</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44438</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44439</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44441</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44446</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44453</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44469</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44477</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>44488</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44491</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44501</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44503</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44512</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44529</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44531</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44536</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44539</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44543</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44544</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44546</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44553</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>44570</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44574</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44580</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44588</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>44592</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>44602</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52746,7 +52746,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52860,7 +52860,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53093,7 +53093,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53314,14 +53314,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 2536-2024</t>
+          <t>A 2517-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53333,8 +53333,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G893" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -53371,14 +53376,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 2517-2024</t>
+          <t>A 2536-2024</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53390,13 +53395,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F894" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G894" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -53440,7 +53440,7 @@
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53547,14 +53547,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3048-2024</t>
+          <t>A 3202-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53567,7 +53567,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -53604,14 +53604,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3205-2024</t>
+          <t>A 3138-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -53661,14 +53661,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3138-2024</t>
+          <t>A 3048-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53718,14 +53718,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3202-2024</t>
+          <t>A 3205-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -53782,7 +53782,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53896,7 +53896,7 @@
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45324</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45329</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45330</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>45331</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,14 +54303,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5514-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54322,13 +54322,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F910" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G910" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -54365,14 +54360,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 5583-2024</t>
+          <t>A 5570-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54384,13 +54379,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F911" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G911" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -54427,14 +54417,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 5514-2024</t>
+          <t>A 5574-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54447,7 +54437,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -54484,14 +54474,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 5570-2024</t>
+          <t>A 5582-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54504,7 +54494,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -54541,14 +54531,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5574-2024</t>
+          <t>A 5583-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54558,6 +54548,11 @@
       <c r="E914" t="inlineStr">
         <is>
           <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="G914" t="n">
@@ -54598,14 +54593,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5582-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54617,8 +54612,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G915" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -54662,7 +54662,7 @@
         <v>45335</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>43555</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44391</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>44425</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44522</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44866</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44967</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>44977</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>44993</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45020</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45039</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45061</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45091</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45204</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45229</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45251</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45258</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45294</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45301</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>43318</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>43336</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>43364</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>43388</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>43391</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43404</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43410</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43413</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43416</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>43425</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43426</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>43431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43434</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43436</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43437</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>43439</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>43441</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>43447</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>43448</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>43450</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>43452</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43454</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>43461</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43462</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43464</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>43471</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>43478</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>43486</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>43487</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>43490</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>43493</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>43498</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>43502</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>43507</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>43508</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>43509</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>43511</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>43522</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>43530</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>43553</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43558</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>43566</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43598</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>43646</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43654</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>43657</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>43669</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>43682</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>43685</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>43689</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>43705</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43707</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43710</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43714</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43716</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43724</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43733</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43747</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43749</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43765</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>43767</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43776</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>43780</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>43782</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>43794</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43808</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43810</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>43811</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>43815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43829</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43837</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43844</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43849</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43850</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43856</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43864</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43866</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43871</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>43873</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>43881</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43892</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>43902</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43912</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43917</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>43933</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>43938</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>43951</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43964</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43973</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43978</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43984</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>43985</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>43986</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>43987</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>43997</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44000</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44002</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44005</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44013</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44049</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44056</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44071</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44073</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44078</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44085</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44088</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44090</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44091</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44096</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44104</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44153</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>44154</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44159</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44161</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44167</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44168</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44172</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44174</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44179</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44181</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44183</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44203</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44207</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44213</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44249</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44274</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44292</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44299</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44305</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44307</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44312</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44319</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44323</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>44326</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44327</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44328</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44335</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44336</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44337</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44349</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44350</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44351</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44371</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44374</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44375</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44376</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44383</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44390</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44393</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44394</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44397</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44399</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44405</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44409</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44413</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>44420</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>44431</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44432</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44438</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44439</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44441</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44446</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44453</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44469</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44477</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>44488</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44491</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44501</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44503</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44512</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44529</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44531</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44536</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44539</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44543</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44544</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44546</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44553</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>44570</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44574</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44580</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44588</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>44592</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>44602</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52746,7 +52746,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52860,7 +52860,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53093,7 +53093,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53321,7 +53321,7 @@
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53440,7 +53440,7 @@
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53547,14 +53547,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3202-2024</t>
+          <t>A 3138-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53567,7 +53567,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -53604,14 +53604,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3138-2024</t>
+          <t>A 3202-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -53668,7 +53668,7 @@
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53725,7 +53725,7 @@
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53896,7 +53896,7 @@
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45324</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45329</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45330</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>45331</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54310,7 +54310,7 @@
         <v>45334</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54367,7 +54367,7 @@
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54424,7 +54424,7 @@
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54481,7 +54481,7 @@
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,14 +54531,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5583-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54593,14 +54593,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5583-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>45335</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z916"/>
+  <dimension ref="A1:Z918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>43555</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44391</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>44425</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44522</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44866</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44967</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>44977</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>44993</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45020</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45039</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45061</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45091</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45204</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45229</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45251</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45258</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45294</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45301</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>43318</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>43336</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>43364</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>43388</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>43391</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43404</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43410</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43413</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43416</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>43425</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43426</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>43431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43434</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43436</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43437</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>43439</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>43441</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>43447</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>43448</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>43450</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>43452</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43454</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>43461</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43462</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43464</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>43471</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>43478</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>43486</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>43487</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>43490</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>43493</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>43498</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>43502</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>43507</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>43508</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>43509</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>43511</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>43522</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>43530</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>43553</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43558</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>43566</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43598</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>43646</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43654</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>43657</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>43669</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>43682</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>43685</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>43689</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>43705</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43707</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43710</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43714</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43716</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43724</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43733</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43747</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43749</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43765</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>43767</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43776</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>43780</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>43782</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>43794</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43808</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43810</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>43811</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>43815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43829</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43837</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43844</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43849</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43850</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43856</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43864</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43866</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43871</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>43873</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>43881</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43892</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>43902</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43912</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43917</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>43933</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>43938</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>43951</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43964</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43973</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43978</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43984</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>43985</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>43986</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>43987</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>43997</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44000</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44002</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44005</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44013</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44049</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44056</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44071</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44073</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44078</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44085</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44088</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44090</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44091</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44096</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44104</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44153</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>44154</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44159</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44161</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44167</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44168</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44172</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44174</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44179</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44181</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44183</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44203</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44207</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44213</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44249</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44274</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44292</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44299</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44305</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44307</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44312</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44319</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44323</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>44326</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44327</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44328</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44335</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44336</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44337</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44349</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44350</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44351</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44371</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44374</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44375</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44376</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44383</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44390</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44393</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44394</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44397</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44399</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44405</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44409</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44413</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>44420</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>44431</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44432</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44438</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44439</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44441</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44446</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44453</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44469</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44477</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>44488</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44491</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44501</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44503</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44512</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44529</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44531</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44536</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44539</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44543</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44544</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44546</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44553</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>44570</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44574</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44580</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44588</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>44592</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>44602</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52746,7 +52746,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52860,7 +52860,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53093,7 +53093,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53321,7 +53321,7 @@
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,14 +53433,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 2822-2024</t>
+          <t>A 2820-2024</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -53490,14 +53490,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 2820-2024</t>
+          <t>A 2822-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -53554,7 +53554,7 @@
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53604,14 +53604,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3202-2024</t>
+          <t>A 3205-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -53668,7 +53668,7 @@
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53718,14 +53718,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3205-2024</t>
+          <t>A 3202-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -53782,7 +53782,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53896,7 +53896,7 @@
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54003,14 +54003,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 4248-2024</t>
+          <t>A 4121-2024</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
-        <v>45324</v>
+        <v>45323</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54023,7 +54023,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -54060,14 +54060,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 4938-2024</t>
+          <t>A 4248-2024</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
-        <v>45329</v>
+        <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54080,7 +54080,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>7.7</v>
+        <v>3.6</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -54117,14 +54117,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4956-2024</t>
+          <t>A 4938-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54136,13 +54136,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F907" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G907" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -54179,14 +54174,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 5231-2024</t>
+          <t>A 4956-2024</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
-        <v>45330</v>
+        <v>45329</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54200,11 +54195,11 @@
       </c>
       <c r="F908" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="G908" t="n">
-        <v>11.2</v>
+        <v>1.1</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -54241,14 +54236,14 @@
     <row r="909" ht="15" customHeight="1">
       <c r="A909" t="inlineStr">
         <is>
-          <t>A 5369-2024</t>
+          <t>A 5231-2024</t>
         </is>
       </c>
       <c r="B909" s="1" t="n">
-        <v>45331</v>
+        <v>45330</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54262,11 +54257,11 @@
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="G909" t="n">
-        <v>2.9</v>
+        <v>11.2</v>
       </c>
       <c r="H909" t="n">
         <v>0</v>
@@ -54303,14 +54298,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 5514-2024</t>
+          <t>A 5369-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
-        <v>45334</v>
+        <v>45331</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54320,6 +54315,11 @@
       <c r="E910" t="inlineStr">
         <is>
           <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="G910" t="n">
@@ -54360,14 +54360,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 5570-2024</t>
+          <t>A 5514-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -54417,14 +54417,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 5574-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54434,6 +54434,11 @@
       <c r="E912" t="inlineStr">
         <is>
           <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="G912" t="n">
@@ -54474,14 +54479,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 5582-2024</t>
+          <t>A 5570-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54494,7 +54499,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -54531,14 +54536,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5574-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54548,11 +54553,6 @@
       <c r="E914" t="inlineStr">
         <is>
           <t>LEKSAND</t>
-        </is>
-      </c>
-      <c r="F914" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="G914" t="n">
@@ -54593,14 +54593,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5583-2024</t>
+          <t>A 5582-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54612,102 +54612,221 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F915" t="inlineStr">
+      <c r="G915" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H915" t="n">
+        <v>0</v>
+      </c>
+      <c r="I915" t="n">
+        <v>0</v>
+      </c>
+      <c r="J915" t="n">
+        <v>0</v>
+      </c>
+      <c r="K915" t="n">
+        <v>0</v>
+      </c>
+      <c r="L915" t="n">
+        <v>0</v>
+      </c>
+      <c r="M915" t="n">
+        <v>0</v>
+      </c>
+      <c r="N915" t="n">
+        <v>0</v>
+      </c>
+      <c r="O915" t="n">
+        <v>0</v>
+      </c>
+      <c r="P915" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q915" t="n">
+        <v>0</v>
+      </c>
+      <c r="R915" s="2" t="inlineStr"/>
+    </row>
+    <row r="916" ht="15" customHeight="1">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>A 5583-2024</t>
+        </is>
+      </c>
+      <c r="B916" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="C916" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="G915" t="n">
+      <c r="G916" t="n">
         <v>0.4</v>
       </c>
-      <c r="H915" t="n">
-        <v>0</v>
-      </c>
-      <c r="I915" t="n">
-        <v>0</v>
-      </c>
-      <c r="J915" t="n">
-        <v>0</v>
-      </c>
-      <c r="K915" t="n">
-        <v>0</v>
-      </c>
-      <c r="L915" t="n">
-        <v>0</v>
-      </c>
-      <c r="M915" t="n">
-        <v>0</v>
-      </c>
-      <c r="N915" t="n">
-        <v>0</v>
-      </c>
-      <c r="O915" t="n">
-        <v>0</v>
-      </c>
-      <c r="P915" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q915" t="n">
-        <v>0</v>
-      </c>
-      <c r="R915" s="2" t="inlineStr"/>
-    </row>
-    <row r="916">
-      <c r="A916" t="inlineStr">
+      <c r="H916" t="n">
+        <v>0</v>
+      </c>
+      <c r="I916" t="n">
+        <v>0</v>
+      </c>
+      <c r="J916" t="n">
+        <v>0</v>
+      </c>
+      <c r="K916" t="n">
+        <v>0</v>
+      </c>
+      <c r="L916" t="n">
+        <v>0</v>
+      </c>
+      <c r="M916" t="n">
+        <v>0</v>
+      </c>
+      <c r="N916" t="n">
+        <v>0</v>
+      </c>
+      <c r="O916" t="n">
+        <v>0</v>
+      </c>
+      <c r="P916" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q916" t="n">
+        <v>0</v>
+      </c>
+      <c r="R916" s="2" t="inlineStr"/>
+    </row>
+    <row r="917" ht="15" customHeight="1">
+      <c r="A917" t="inlineStr">
         <is>
           <t>A 5900-2024</t>
         </is>
       </c>
-      <c r="B916" s="1" t="n">
+      <c r="B917" s="1" t="n">
         <v>45335</v>
       </c>
-      <c r="C916" s="1" t="n">
-        <v>45340</v>
-      </c>
-      <c r="D916" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E916" t="inlineStr">
-        <is>
-          <t>LEKSAND</t>
-        </is>
-      </c>
-      <c r="G916" t="n">
+      <c r="C917" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="G917" t="n">
         <v>0.8</v>
       </c>
-      <c r="H916" t="n">
-        <v>0</v>
-      </c>
-      <c r="I916" t="n">
-        <v>0</v>
-      </c>
-      <c r="J916" t="n">
-        <v>0</v>
-      </c>
-      <c r="K916" t="n">
-        <v>0</v>
-      </c>
-      <c r="L916" t="n">
-        <v>0</v>
-      </c>
-      <c r="M916" t="n">
-        <v>0</v>
-      </c>
-      <c r="N916" t="n">
-        <v>0</v>
-      </c>
-      <c r="O916" t="n">
-        <v>0</v>
-      </c>
-      <c r="P916" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q916" t="n">
-        <v>0</v>
-      </c>
-      <c r="R916" s="2" t="inlineStr"/>
+      <c r="H917" t="n">
+        <v>0</v>
+      </c>
+      <c r="I917" t="n">
+        <v>0</v>
+      </c>
+      <c r="J917" t="n">
+        <v>0</v>
+      </c>
+      <c r="K917" t="n">
+        <v>0</v>
+      </c>
+      <c r="L917" t="n">
+        <v>0</v>
+      </c>
+      <c r="M917" t="n">
+        <v>0</v>
+      </c>
+      <c r="N917" t="n">
+        <v>0</v>
+      </c>
+      <c r="O917" t="n">
+        <v>0</v>
+      </c>
+      <c r="P917" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q917" t="n">
+        <v>0</v>
+      </c>
+      <c r="R917" s="2" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>A 6758-2024</t>
+        </is>
+      </c>
+      <c r="B918" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C918" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G918" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H918" t="n">
+        <v>0</v>
+      </c>
+      <c r="I918" t="n">
+        <v>0</v>
+      </c>
+      <c r="J918" t="n">
+        <v>0</v>
+      </c>
+      <c r="K918" t="n">
+        <v>0</v>
+      </c>
+      <c r="L918" t="n">
+        <v>0</v>
+      </c>
+      <c r="M918" t="n">
+        <v>0</v>
+      </c>
+      <c r="N918" t="n">
+        <v>0</v>
+      </c>
+      <c r="O918" t="n">
+        <v>0</v>
+      </c>
+      <c r="P918" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q918" t="n">
+        <v>0</v>
+      </c>
+      <c r="R918" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>43555</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44391</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>44425</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44522</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44866</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44967</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>44977</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>44993</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45020</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45039</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45061</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45091</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45204</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45229</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45251</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45258</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45294</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45301</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>43318</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>43336</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>43364</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>43388</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>43391</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43404</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43410</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43413</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43416</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>43425</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43426</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>43431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43434</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43436</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43437</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>43439</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>43441</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>43447</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>43448</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>43450</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>43452</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43454</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>43461</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43462</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43464</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>43471</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>43478</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>43486</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>43487</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>43490</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>43493</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>43498</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>43502</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>43507</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>43508</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>43509</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>43511</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>43522</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>43530</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>43553</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43558</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>43566</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43598</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>43646</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43654</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>43657</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>43669</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>43682</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>43685</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>43689</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>43705</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43707</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43710</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43714</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43716</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43724</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43733</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43747</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43749</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43765</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>43767</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43776</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>43780</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>43782</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>43794</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43808</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43810</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>43811</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>43815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43829</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43837</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43844</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43849</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43850</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43856</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43864</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43866</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43871</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>43873</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>43881</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43892</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>43902</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43912</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43917</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>43933</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>43938</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>43951</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43964</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43973</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43978</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43984</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>43985</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>43986</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>43987</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>43997</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44000</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44002</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44005</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44013</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44049</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44056</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44071</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44073</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44078</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44085</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44088</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44090</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44091</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44096</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44104</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44153</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>44154</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44159</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44161</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44167</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44168</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44172</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44174</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44179</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44181</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44183</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44203</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44207</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44213</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44249</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44274</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44292</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44299</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44305</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44307</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44312</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44319</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44323</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>44326</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44327</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44328</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44335</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44336</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44337</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44349</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44350</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44351</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44371</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44374</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44375</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44376</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44383</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44390</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44393</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44394</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44397</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44399</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44405</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44409</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44413</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>44420</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>44431</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44432</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44438</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44439</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44441</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44446</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44453</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44469</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44477</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>44488</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44491</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44501</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44503</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44512</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44529</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44531</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44536</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44539</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44543</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44544</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44546</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44553</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>44570</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44574</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44580</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44588</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>44592</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>44602</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52746,7 +52746,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52860,7 +52860,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53093,7 +53093,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53314,14 +53314,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 2517-2024</t>
+          <t>A 2536-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53333,13 +53333,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F893" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G893" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -53376,14 +53371,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 2536-2024</t>
+          <t>A 2517-2024</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53395,8 +53390,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G894" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -53440,7 +53440,7 @@
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53554,7 +53554,7 @@
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53668,7 +53668,7 @@
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53725,7 +53725,7 @@
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53832,14 +53832,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3901-2024</t>
+          <t>A 3970-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53852,7 +53852,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -53889,14 +53889,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3970-2024</t>
+          <t>A 3974-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53909,7 +53909,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -53946,14 +53946,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 3974-2024</t>
+          <t>A 3901-2024</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45323</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54117,14 +54117,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4938-2024</t>
+          <t>A 4956-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54136,8 +54136,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G907" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -54174,14 +54179,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 4956-2024</t>
+          <t>A 4938-2024</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54193,13 +54198,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F908" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G908" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -54243,7 +54243,7 @@
         <v>45330</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>45331</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54367,7 +54367,7 @@
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,14 +54417,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5583-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54479,14 +54479,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 5570-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54498,8 +54498,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G913" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -54536,14 +54541,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5574-2024</t>
+          <t>A 5570-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54556,7 +54561,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -54593,14 +54598,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5582-2024</t>
+          <t>A 5574-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54613,7 +54618,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -54650,14 +54655,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5583-2024</t>
+          <t>A 5582-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54669,13 +54674,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F916" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G916" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -54719,7 +54719,7 @@
         <v>45335</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>45342</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>43555</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44391</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>44425</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44522</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44866</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44967</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>44977</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>44993</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45020</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45039</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45061</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45091</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45204</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45229</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45251</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45258</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45294</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45301</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>43318</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>43336</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>43364</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>43388</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>43391</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43404</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43410</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43413</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43416</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>43425</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43426</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>43431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43434</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43436</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43437</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>43439</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>43441</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>43447</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>43448</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>43450</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>43452</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43454</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>43461</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43462</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43464</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>43471</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>43478</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>43486</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>43487</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>43490</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>43493</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>43498</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>43502</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>43507</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>43508</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>43509</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>43511</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>43522</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>43530</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>43553</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43558</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>43566</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43598</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>43646</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43654</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>43657</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>43669</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>43682</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>43685</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>43689</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>43705</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43707</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43710</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43714</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43716</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43724</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43733</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43747</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43749</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43765</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>43767</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43776</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>43780</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>43782</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>43794</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43808</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43810</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>43811</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>43815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>43829</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>43837</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>43844</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>43849</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>43850</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>43856</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>43864</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>43866</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>43871</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>43873</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>43881</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>43892</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>43902</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43912</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43917</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>43933</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>43938</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>43951</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43964</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43973</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43978</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43984</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>43985</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>43986</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>43987</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>43997</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44000</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44002</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44005</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44013</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44049</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44056</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44071</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44073</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44078</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44085</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44088</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44090</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44091</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44096</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44104</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44153</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>44154</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44159</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44161</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44167</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44168</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44172</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44174</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44179</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44181</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44183</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44203</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44207</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44213</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44249</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44274</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44292</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44299</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44305</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44307</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44312</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44319</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44323</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>44326</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44327</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44328</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44335</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44336</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44337</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44349</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44350</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44351</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44371</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44374</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44375</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44376</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44383</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44390</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44393</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44394</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44397</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44399</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44405</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44409</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44413</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>44420</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>44431</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44432</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44438</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44439</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44441</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44446</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44453</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44469</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44477</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>44488</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44491</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44501</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44503</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44512</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44529</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44531</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44536</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44539</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44543</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44544</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44546</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44553</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>44570</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44574</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44580</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44588</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>44592</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>44602</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52746,7 +52746,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52860,7 +52860,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53093,7 +53093,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53321,7 +53321,7 @@
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53378,7 +53378,7 @@
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53440,7 +53440,7 @@
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53547,14 +53547,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3138-2024</t>
+          <t>A 3205-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53567,7 +53567,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -53604,14 +53604,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3205-2024</t>
+          <t>A 3138-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -53668,7 +53668,7 @@
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53725,7 +53725,7 @@
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53896,7 +53896,7 @@
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45323</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45329</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>45330</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>45331</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54367,7 +54367,7 @@
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,14 +54417,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 5583-2024</t>
+          <t>A 5570-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54436,13 +54436,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F912" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G912" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -54479,14 +54474,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5574-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54496,11 +54491,6 @@
       <c r="E913" t="inlineStr">
         <is>
           <t>LEKSAND</t>
-        </is>
-      </c>
-      <c r="F913" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="G913" t="n">
@@ -54541,14 +54531,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5570-2024</t>
+          <t>A 5582-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54561,7 +54551,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -54598,14 +54588,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5574-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54615,6 +54605,11 @@
       <c r="E915" t="inlineStr">
         <is>
           <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="G915" t="n">
@@ -54655,14 +54650,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5582-2024</t>
+          <t>A 5583-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54674,8 +54669,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G916" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -54719,7 +54719,7 @@
         <v>45335</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>45342</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>44602</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>43555</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44391</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44425</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44522</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>44866</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44967</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44977</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44993</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45020</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45039</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45061</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45091</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45204</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45229</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45251</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45258</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45294</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45301</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>43318</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>43362</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>43364</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>43388</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>43391</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>43404</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>43408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>43410</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>43413</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>43416</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>43423</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>43425</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>43426</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>43433</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>43434</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43436</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>43437</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>43439</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>43447</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>43448</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>43450</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43452</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43454</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>43461</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>43462</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>43464</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>43471</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>43478</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>43486</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>43487</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>43490</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>43498</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>43502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>43507</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>43508</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43509</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>43510</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>43511</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>43522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>43523</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>43530</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>43535</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>43557</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>43558</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>43566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>43598</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>43600</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>43646</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>43654</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>43657</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>43669</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>43682</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>43685</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>43689</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>43707</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43710</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>43714</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>43716</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>43719</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>43724</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>43733</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>43735</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>43746</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>43747</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>43749</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>43765</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>43767</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>43776</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>43780</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>43782</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43794</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43808</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43810</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43811</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43829</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43837</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43844</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>43849</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>43850</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>43856</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>43864</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>43866</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43871</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43873</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43881</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43892</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43895</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43902</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43912</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43917</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43933</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43938</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43951</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>43964</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>43973</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>43978</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>43984</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>43985</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>43986</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>43987</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>43997</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44000</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44002</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44005</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44013</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44049</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44056</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44071</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44073</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44078</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44085</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44088</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44090</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44091</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44096</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44104</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44153</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44154</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44159</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44161</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44167</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44168</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44172</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44174</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44179</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44181</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44183</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44203</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44207</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44213</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44249</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44274</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>44292</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44299</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44305</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44307</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44312</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44319</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44323</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44326</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44327</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44328</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44335</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44336</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>44337</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44349</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44350</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44351</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44374</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44375</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44376</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44383</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44390</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>44393</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44394</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44397</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44399</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44405</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44409</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44413</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>44420</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44431</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44432</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44438</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44439</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44441</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44446</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44453</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44469</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44477</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44488</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44491</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44501</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44503</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44512</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44529</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44531</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44533</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44536</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44539</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44543</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44544</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44546</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44553</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44570</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44574</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44580</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44588</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44592</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43956,7 +43956,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48784,7 +48784,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53815,7 +53815,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53865,14 +53865,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3970-2024</t>
+          <t>A 3901-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -53922,14 +53922,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3974-2024</t>
+          <t>A 3970-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -53979,14 +53979,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 3901-2024</t>
+          <t>A 3974-2024</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>45323</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54150,14 +54150,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4938-2024</t>
+          <t>A 4956-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54169,8 +54169,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G907" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -54207,14 +54212,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 4956-2024</t>
+          <t>A 4938-2024</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54226,13 +54231,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F908" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G908" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -54276,7 +54276,7 @@
         <v>45330</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45331</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54393,14 +54393,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 5514-2024</t>
+          <t>A 5570-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -54450,14 +54450,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5574-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54467,11 +54467,6 @@
       <c r="E912" t="inlineStr">
         <is>
           <t>LEKSAND</t>
-        </is>
-      </c>
-      <c r="F912" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="G912" t="n">
@@ -54512,14 +54507,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 5583-2024</t>
+          <t>A 5582-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,13 +54526,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F913" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G913" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -54574,14 +54564,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5570-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54593,8 +54583,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G914" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -54631,14 +54626,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5574-2024</t>
+          <t>A 5514-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54651,7 +54646,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -54688,14 +54683,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5582-2024</t>
+          <t>A 5583-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,8 +54702,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G916" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -54752,7 +54752,7 @@
         <v>45335</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>45342</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>45345</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>44602</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>43555</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44391</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44425</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44522</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>44866</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44967</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44977</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44993</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45020</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45039</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45061</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45091</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45204</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45229</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45251</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45258</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45294</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45301</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>43318</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>43362</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>43364</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>43388</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>43391</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>43404</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>43408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>43410</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>43413</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>43416</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>43423</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>43425</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>43426</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>43433</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>43434</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43436</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>43437</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>43439</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>43447</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>43448</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>43450</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43452</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43454</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>43461</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>43462</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>43464</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>43471</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>43478</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>43486</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>43487</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>43490</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>43498</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>43502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>43507</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>43508</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43509</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>43510</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>43511</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>43522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>43523</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>43530</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>43535</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>43557</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>43558</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>43566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>43598</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>43600</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>43646</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>43654</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>43657</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>43669</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>43682</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>43685</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>43689</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>43707</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43710</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>43714</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>43716</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>43719</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>43724</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>43733</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>43735</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>43746</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>43747</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>43749</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>43765</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>43767</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>43776</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>43780</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>43782</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43794</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43808</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43810</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43811</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43829</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43837</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43844</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>43849</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>43850</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>43856</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>43864</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>43866</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43871</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43873</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43881</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43892</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43895</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43902</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43912</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43917</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43933</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43938</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43951</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>43964</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>43973</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>43978</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>43984</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>43985</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>43986</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>43987</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>43997</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44000</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44002</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44005</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44013</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44049</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44056</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44071</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44073</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44078</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44085</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44088</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44090</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44091</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44096</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44104</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44153</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44154</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44159</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44161</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44167</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44168</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44172</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44174</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44179</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44181</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44183</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44203</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44207</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44213</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44249</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44274</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>44292</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44299</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44305</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44307</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44312</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44319</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44323</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44326</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44327</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44328</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44335</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44336</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>44337</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44349</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44350</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44351</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44374</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44375</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44376</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44383</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44390</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>44393</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44394</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44397</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44399</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44405</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44409</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44413</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>44420</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44431</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44432</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44438</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44439</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44441</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44446</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44453</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44469</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44477</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44488</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44491</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44501</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44503</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44512</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44529</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44531</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44533</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44536</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44539</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44543</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44544</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44546</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44553</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44570</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44574</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44580</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44588</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44592</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43956,7 +43956,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48784,7 +48784,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53815,7 +53815,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53865,14 +53865,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3901-2024</t>
+          <t>A 3970-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -53922,14 +53922,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3970-2024</t>
+          <t>A 3974-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -53979,14 +53979,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 3974-2024</t>
+          <t>A 3901-2024</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>45323</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54150,14 +54150,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4956-2024</t>
+          <t>A 4938-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54169,13 +54169,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F907" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G907" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -54212,14 +54207,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 4938-2024</t>
+          <t>A 4956-2024</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54231,8 +54226,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G908" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -54276,7 +54276,7 @@
         <v>45330</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45331</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54393,14 +54393,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 5570-2024</t>
+          <t>A 5514-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -54450,14 +54450,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 5574-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54467,6 +54467,11 @@
       <c r="E912" t="inlineStr">
         <is>
           <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="G912" t="n">
@@ -54507,14 +54512,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 5582-2024</t>
+          <t>A 5570-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54527,7 +54532,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -54564,14 +54569,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5574-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54581,11 +54586,6 @@
       <c r="E914" t="inlineStr">
         <is>
           <t>LEKSAND</t>
-        </is>
-      </c>
-      <c r="F914" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="G914" t="n">
@@ -54626,14 +54626,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5514-2024</t>
+          <t>A 5582-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -54690,7 +54690,7 @@
         <v>45334</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>45335</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>45342</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>45345</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>44602</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>43555</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44391</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44425</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44522</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>44866</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44967</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44977</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44993</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45020</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45039</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45061</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45091</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45204</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45229</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45251</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45258</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45294</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45301</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>43318</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>43362</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>43364</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>43388</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>43391</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>43404</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>43408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>43410</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>43413</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>43416</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>43423</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>43425</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>43426</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>43433</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>43434</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43436</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>43437</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>43439</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>43447</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>43448</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>43450</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43452</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43454</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>43461</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>43462</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>43464</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>43471</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>43478</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>43486</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>43487</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>43490</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>43498</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>43502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>43507</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>43508</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43509</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>43510</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>43511</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>43522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>43523</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>43530</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>43535</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>43557</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>43558</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>43566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>43598</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>43600</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>43646</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>43654</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>43657</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>43669</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>43682</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>43685</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>43689</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>43707</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43710</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>43714</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>43716</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>43719</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>43724</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>43733</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>43735</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>43746</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>43747</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>43749</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>43765</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>43767</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>43776</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>43780</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>43782</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43794</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43808</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43810</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43811</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43829</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43837</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43844</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>43849</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>43850</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>43856</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>43864</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>43866</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43871</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43873</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43881</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43892</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43895</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43902</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43912</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43917</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43933</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43938</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43951</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>43964</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>43973</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>43978</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>43984</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>43985</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>43986</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>43987</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>43997</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44000</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44002</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44005</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44013</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44049</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44056</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44071</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44073</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44078</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44085</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44088</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44090</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44091</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44096</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44104</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44153</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44154</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44159</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44161</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44167</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44168</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44172</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44174</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44179</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44181</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44183</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44203</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44207</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44213</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44249</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44274</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>44292</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44299</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44305</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44307</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44312</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44319</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44323</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44326</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44327</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44328</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44335</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44336</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>44337</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44349</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44350</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44351</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44374</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44375</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44376</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44383</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44390</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>44393</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44394</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44397</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44399</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44405</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44409</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44413</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>44420</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44431</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44432</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44438</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44439</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44441</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44446</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44453</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44469</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44477</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44488</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44491</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44501</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44503</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44512</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44529</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44531</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44533</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44536</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44539</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44543</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44544</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44546</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44553</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44570</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44574</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44580</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44588</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44592</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43956,7 +43956,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48784,7 +48784,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53815,7 +53815,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53865,14 +53865,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3970-2024</t>
+          <t>A 3901-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -53922,14 +53922,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3974-2024</t>
+          <t>A 3970-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -53979,14 +53979,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 3901-2024</t>
+          <t>A 3974-2024</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>45323</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54150,14 +54150,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4938-2024</t>
+          <t>A 4956-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54169,8 +54169,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G907" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -54207,14 +54212,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 4956-2024</t>
+          <t>A 4938-2024</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54226,13 +54231,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F908" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G908" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -54276,7 +54276,7 @@
         <v>45330</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45331</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54393,14 +54393,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 5514-2024</t>
+          <t>A 5583-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54412,8 +54412,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G911" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -54450,14 +54455,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5514-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54469,13 +54474,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F912" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G912" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -54519,7 +54519,7 @@
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54683,14 +54683,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5583-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>45335</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>45342</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>45345</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z919"/>
+  <dimension ref="A1:Z923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>44602</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>43555</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44391</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44425</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44522</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>44866</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44967</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44977</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44993</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45020</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45039</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45061</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45091</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45204</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45229</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45251</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45258</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45294</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45301</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>43318</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>43362</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>43364</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>43388</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>43391</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>43404</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>43408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>43410</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>43413</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>43416</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>43423</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>43425</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>43426</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>43433</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>43434</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43436</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>43437</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>43439</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>43447</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>43448</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>43450</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43452</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43454</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>43461</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>43462</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>43464</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>43471</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>43478</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>43486</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>43487</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>43490</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>43498</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>43502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>43507</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>43508</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43509</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>43510</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>43511</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>43522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>43523</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>43530</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>43535</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>43557</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>43558</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>43566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>43598</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>43600</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>43646</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>43654</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>43657</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>43669</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>43682</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>43685</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>43689</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>43707</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43710</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>43714</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>43716</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>43719</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>43724</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>43733</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>43735</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>43746</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>43747</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>43749</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>43765</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>43767</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>43776</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>43780</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>43782</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43794</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43808</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43810</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43811</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43829</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43837</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43844</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>43849</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>43850</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>43856</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>43864</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>43866</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43871</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43873</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43881</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43892</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43895</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43902</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43912</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43917</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43933</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43938</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43951</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>43964</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>43973</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>43978</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>43984</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>43985</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>43986</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>43987</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>43997</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44000</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44002</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44005</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44013</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44049</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44056</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44071</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44073</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44078</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44085</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44088</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44090</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44091</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44096</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44104</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44153</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44154</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44159</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44161</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44167</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44168</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44172</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44174</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44179</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44181</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44183</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44203</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44207</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44213</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44249</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44274</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>44292</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44299</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44305</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44307</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44312</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44319</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44323</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44326</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44327</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44328</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44335</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44336</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>44337</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44349</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44350</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44351</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44374</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44375</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44376</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44383</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44390</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>44393</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44394</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44397</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44399</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44405</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44409</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44413</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>44420</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44431</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44432</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44438</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44439</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44441</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44446</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44453</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44469</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44477</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44488</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44491</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44501</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44503</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44512</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44529</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44531</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44533</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44536</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44539</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44543</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44544</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44546</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44553</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44570</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44574</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44580</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44588</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44592</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43956,7 +43956,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48784,7 +48784,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53815,7 +53815,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53929,7 +53929,7 @@
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53986,7 +53986,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>45323</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54157,7 +54157,7 @@
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45329</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45330</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45331</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54393,14 +54393,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 5583-2024</t>
+          <t>A 5514-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54412,13 +54412,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F911" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G911" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -54455,14 +54450,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 5514-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,8 +54469,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G912" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -54519,7 +54519,7 @@
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54683,14 +54683,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5583-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>45335</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>45342</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
       </c>
       <c r="R918" s="2" t="inlineStr"/>
     </row>
-    <row r="919">
+    <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
           <t>A 7417-2024</t>
@@ -54871,7 +54871,7 @@
         <v>45345</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54917,6 +54917,234 @@
         <v>0</v>
       </c>
       <c r="R919" s="2" t="inlineStr"/>
+    </row>
+    <row r="920" ht="15" customHeight="1">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>A 7775-2024</t>
+        </is>
+      </c>
+      <c r="B920" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C920" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="G920" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H920" t="n">
+        <v>0</v>
+      </c>
+      <c r="I920" t="n">
+        <v>0</v>
+      </c>
+      <c r="J920" t="n">
+        <v>0</v>
+      </c>
+      <c r="K920" t="n">
+        <v>0</v>
+      </c>
+      <c r="L920" t="n">
+        <v>0</v>
+      </c>
+      <c r="M920" t="n">
+        <v>0</v>
+      </c>
+      <c r="N920" t="n">
+        <v>0</v>
+      </c>
+      <c r="O920" t="n">
+        <v>0</v>
+      </c>
+      <c r="P920" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q920" t="n">
+        <v>0</v>
+      </c>
+      <c r="R920" s="2" t="inlineStr"/>
+    </row>
+    <row r="921" ht="15" customHeight="1">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>A 7768-2024</t>
+        </is>
+      </c>
+      <c r="B921" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C921" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="G921" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H921" t="n">
+        <v>0</v>
+      </c>
+      <c r="I921" t="n">
+        <v>0</v>
+      </c>
+      <c r="J921" t="n">
+        <v>0</v>
+      </c>
+      <c r="K921" t="n">
+        <v>0</v>
+      </c>
+      <c r="L921" t="n">
+        <v>0</v>
+      </c>
+      <c r="M921" t="n">
+        <v>0</v>
+      </c>
+      <c r="N921" t="n">
+        <v>0</v>
+      </c>
+      <c r="O921" t="n">
+        <v>0</v>
+      </c>
+      <c r="P921" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q921" t="n">
+        <v>0</v>
+      </c>
+      <c r="R921" s="2" t="inlineStr"/>
+    </row>
+    <row r="922" ht="15" customHeight="1">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>A 7773-2024</t>
+        </is>
+      </c>
+      <c r="B922" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C922" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="G922" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H922" t="n">
+        <v>0</v>
+      </c>
+      <c r="I922" t="n">
+        <v>0</v>
+      </c>
+      <c r="J922" t="n">
+        <v>0</v>
+      </c>
+      <c r="K922" t="n">
+        <v>0</v>
+      </c>
+      <c r="L922" t="n">
+        <v>0</v>
+      </c>
+      <c r="M922" t="n">
+        <v>0</v>
+      </c>
+      <c r="N922" t="n">
+        <v>0</v>
+      </c>
+      <c r="O922" t="n">
+        <v>0</v>
+      </c>
+      <c r="P922" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q922" t="n">
+        <v>0</v>
+      </c>
+      <c r="R922" s="2" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>A 7827-2024</t>
+        </is>
+      </c>
+      <c r="B923" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C923" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="G923" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H923" t="n">
+        <v>0</v>
+      </c>
+      <c r="I923" t="n">
+        <v>0</v>
+      </c>
+      <c r="J923" t="n">
+        <v>0</v>
+      </c>
+      <c r="K923" t="n">
+        <v>0</v>
+      </c>
+      <c r="L923" t="n">
+        <v>0</v>
+      </c>
+      <c r="M923" t="n">
+        <v>0</v>
+      </c>
+      <c r="N923" t="n">
+        <v>0</v>
+      </c>
+      <c r="O923" t="n">
+        <v>0</v>
+      </c>
+      <c r="P923" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q923" t="n">
+        <v>0</v>
+      </c>
+      <c r="R923" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z923"/>
+  <dimension ref="A1:Z924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>44602</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>43555</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44391</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44425</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44522</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>44866</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44967</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44977</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44993</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45020</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45039</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45061</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45091</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45204</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45229</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45251</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45258</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45294</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45301</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>43318</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>43362</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>43364</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>43388</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>43391</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>43404</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>43408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>43410</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>43413</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>43416</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>43423</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>43425</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>43426</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>43433</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>43434</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43436</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>43437</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>43439</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>43447</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>43448</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>43450</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43452</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43454</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>43461</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>43462</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>43464</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>43471</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>43478</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>43486</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>43487</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>43490</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>43498</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>43502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>43507</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>43508</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43509</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>43510</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>43511</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>43522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>43523</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>43530</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>43535</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>43557</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>43558</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>43566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>43598</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>43600</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>43646</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>43654</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>43657</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>43669</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>43682</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>43685</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>43689</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>43707</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43710</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>43714</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>43716</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>43719</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>43724</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>43733</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>43735</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>43746</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>43747</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>43749</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>43765</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>43767</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>43776</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>43780</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>43782</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43794</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43808</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43810</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43811</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43829</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43837</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43844</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>43849</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>43850</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>43856</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>43864</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>43866</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43871</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43873</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43881</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43892</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43895</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43902</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43912</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43917</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43933</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43938</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43951</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>43964</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>43973</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>43978</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>43984</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>43985</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>43986</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>43987</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>43997</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44000</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44002</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44005</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44013</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44049</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44056</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44071</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44073</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44078</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44085</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44088</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44090</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44091</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44096</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44104</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44153</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44154</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44159</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44161</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44167</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44168</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44172</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44174</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44179</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44181</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44183</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44203</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44207</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44213</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44249</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44274</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>44292</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44299</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44305</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44307</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44312</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44319</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44323</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44326</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44327</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44328</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44335</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44336</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>44337</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44349</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44350</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44351</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44374</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44375</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44376</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44383</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44390</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>44393</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44394</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44397</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44399</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44405</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44409</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44413</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>44420</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44431</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44432</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44438</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44439</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44441</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44446</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44453</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44469</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44477</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44488</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44491</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44501</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44503</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44512</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44529</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44531</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44533</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44536</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44539</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44543</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44544</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44546</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44553</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44570</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44574</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44580</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44588</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44592</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43956,7 +43956,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48784,7 +48784,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45308</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>45309</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45309</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         <v>45313</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45313</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>45314</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>45314</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>45316</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45316</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45316</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>45316</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53815,7 +53815,7 @@
         <v>45317</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45322</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53929,7 +53929,7 @@
         <v>45322</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53986,7 +53986,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>45323</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54150,14 +54150,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4956-2024</t>
+          <t>A 4938-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54169,13 +54169,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F907" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G907" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -54212,14 +54207,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 4938-2024</t>
+          <t>A 4956-2024</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54231,8 +54226,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G908" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -54276,7 +54276,7 @@
         <v>45330</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45331</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54393,14 +54393,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 5514-2024</t>
+          <t>A 5583-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54412,8 +54412,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G911" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -54450,14 +54455,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 5584-2024</t>
+          <t>A 5514-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54469,13 +54474,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F912" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G912" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -54512,14 +54512,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 5570-2024</t>
+          <t>A 5584-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,8 +54531,13 @@
           <t>LEKSAND</t>
         </is>
       </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G913" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -54569,14 +54574,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5574-2024</t>
+          <t>A 5570-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54589,7 +54594,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -54626,14 +54631,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5582-2024</t>
+          <t>A 5574-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54646,7 +54651,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -54683,14 +54688,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5583-2024</t>
+          <t>A 5582-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54702,13 +54707,8 @@
           <t>LEKSAND</t>
         </is>
       </c>
-      <c r="F916" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G916" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -54752,7 +54752,7 @@
         <v>45335</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>45342</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>45345</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54921,14 +54921,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 7775-2024</t>
+          <t>A 7768-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54941,7 +54941,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -54978,14 +54978,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 7768-2024</t>
+          <t>A 7773-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54998,7 +54998,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -55035,14 +55035,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 7773-2024</t>
+          <t>A 7775-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -55089,7 +55089,7 @@
       </c>
       <c r="R922" s="2" t="inlineStr"/>
     </row>
-    <row r="923">
+    <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
           <t>A 7827-2024</t>
@@ -55099,7 +55099,7 @@
         <v>45349</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55145,6 +55145,63 @@
         <v>0</v>
       </c>
       <c r="R923" s="2" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>A 7861-2024</t>
+        </is>
+      </c>
+      <c r="B924" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C924" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="G924" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H924" t="n">
+        <v>0</v>
+      </c>
+      <c r="I924" t="n">
+        <v>0</v>
+      </c>
+      <c r="J924" t="n">
+        <v>0</v>
+      </c>
+      <c r="K924" t="n">
+        <v>0</v>
+      </c>
+      <c r="L924" t="n">
+        <v>0</v>
+      </c>
+      <c r="M924" t="n">
+        <v>0</v>
+      </c>
+      <c r="N924" t="n">
+        <v>0</v>
+      </c>
+      <c r="O924" t="n">
+        <v>0</v>
+      </c>
+      <c r="P924" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q924" t="n">
+        <v>0</v>
+      </c>
+      <c r="R924" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z924"/>
+  <dimension ref="A1:Z926"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44510</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44876</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>43783</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>43783</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44992</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44834</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44866</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>43405</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45156</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45201</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45205</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>43780</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>44053</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44475</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>44602</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>43555</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44391</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44425</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44522</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>44866</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44967</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44977</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44993</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45020</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45039</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45061</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45091</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45204</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45229</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45251</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45258</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45294</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45301</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>43318</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>43318</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>43362</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>43364</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>43388</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>43391</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>43404</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>43408</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>43410</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>43413</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>43416</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>43423</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>43423</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>43425</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>43426</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>43433</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>43434</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43436</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43436</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43437</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>43437</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>43439</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>43447</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>43448</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>43450</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43452</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43452</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43454</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>43461</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>43462</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>43464</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>43471</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>43478</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>43486</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>43487</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>43487</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>43490</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>43498</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>43502</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>43502</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>43507</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>43508</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43509</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>43510</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>43511</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>43522</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>43523</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>43530</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>43535</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>43557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>43557</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>43558</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>43566</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>43566</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>43598</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>43598</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>43600</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>43646</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>43654</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>43657</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>43657</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>43669</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>43682</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>43682</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>43685</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>43689</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>43707</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43710</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>43714</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>43716</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>43719</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>43719</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>43724</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>43733</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>43735</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>43746</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>43747</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>43749</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>43765</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>43767</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>43776</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>43780</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>43782</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>43782</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43794</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43808</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43810</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43811</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43829</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43837</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43844</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>43849</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>43850</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>43856</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>43864</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>43864</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>43866</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43871</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43873</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43881</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43892</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43895</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43902</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43902</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43902</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43912</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43917</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43933</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43938</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43951</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>43964</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>43973</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>43978</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>43984</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>43985</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>43986</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>43987</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>43997</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44000</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44002</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44002</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44005</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44013</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44049</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44056</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44071</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44071</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44073</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44078</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44085</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44088</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44090</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44091</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44096</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44104</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44104</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44153</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44154</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44159</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44161</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44167</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44168</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44172</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44174</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44179</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44181</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44183</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44203</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44207</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44213</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44249</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44249</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44274</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>44292</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44299</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44305</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44307</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44312</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44319</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44323</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44323</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44323</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44326</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44327</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44327</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44328</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44335</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44336</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>44337</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44349</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44350</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44351</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44374</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44375</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44376</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44383</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44383</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44383</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44390</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>44393</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44394</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44397</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44399</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44405</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44409</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44413</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>44420</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44431</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44432</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44438</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44439</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44441</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44446</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44453</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44469</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44477</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44488</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44491</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44501</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44501</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44501</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44503</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44512</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44529</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44529</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44531</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44533</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44533</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>44536</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44536</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44539</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44543</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44544</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44544</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44546</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44546</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44553</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44570</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44574</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44580</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44588</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44592</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44613</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44628</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>44630</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>44651</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44656</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>44670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44671</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44676</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44690</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44690</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44693</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44693</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44697</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44698</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44711</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44711</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44711</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44714</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44714</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>44719</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44731</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44735</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44740</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44746</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>44749</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44749</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>44749</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44750</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44750</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44761</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44776</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44777</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44781</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44782</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44784</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44785</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>44792</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44792</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44797</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>44797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44802</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44802</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44808</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44811</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44812</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44812</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44816</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44818</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44820</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44824</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44824</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>44829</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>44834</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44834</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44837</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44837</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44837</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>44839</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44840</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44846</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>44846</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44851</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44851</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44853</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44861</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44861</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44862</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>44865</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44866</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44866</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44866</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44867</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44869</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44869</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44869</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44869</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44872</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44875</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44877</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44880</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44881</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44890</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>44896</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>44896</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>44902</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>44903</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44909</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44909</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44909</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44911</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>44912</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44914</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44915</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44917</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44917</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44918</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44929</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44929</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44929</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44929</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44931</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44937</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44948</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44949</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44951</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44951</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>44953</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>44959</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44959</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44959</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44959</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44962</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>44964</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44966</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44967</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44971</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44971</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44973</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44974</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44974</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44974</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44974</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44974</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>44974</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>44977</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44978</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44978</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44978</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>44978</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>44980</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44980</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44985</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44986</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>44986</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>44987</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44987</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44987</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44988</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44988</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44988</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44990</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44990</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44991</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44991</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44991</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44991</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44991</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44992</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44992</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44992</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44992</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44992</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44992</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44992</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44992</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44992</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44993</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44993</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>44993</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>44993</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44993</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44993</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>44994</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44994</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44994</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44998</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44998</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>44998</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44998</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44998</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44999</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45001</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45001</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45001</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45001</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45001</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45001</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45002</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45004</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45005</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45005</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45005</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45012</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45014</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45015</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45015</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45015</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45015</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45016</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45019</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45019</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45020</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45020</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45022</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45022</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45027</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45027</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45027</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45027</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45027</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45028</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45028</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45030</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45033</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45033</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45033</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45034</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45034</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45034</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45034</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45034</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>45034</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45035</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45035</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45035</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45035</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45036</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45040</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45041</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45042</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45042</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45043</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45043</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45043</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45044</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45044</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45048</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45049</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45049</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45049</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45061</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45061</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45061</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45062</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45068</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45068</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45068</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45068</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45069</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45069</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45071</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45071</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45075</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45076</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45076</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45078</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45084</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45084</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45084</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45086</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45086</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45089</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45089</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45089</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45090</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45090</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45090</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45091</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45091</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45091</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45093</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45093</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45093</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45093</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45093</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45095</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45095</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45095</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45095</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45095</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45096</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45096</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45097</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45097</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45097</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45098</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45103</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45103</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45104</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>45104</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45104</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45104</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45104</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45104</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45105</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45105</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45105</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45107</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45107</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45108</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45109</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45110</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45110</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45110</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45110</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45110</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45112</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45112</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45112</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45112</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45113</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45113</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45113</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>45113</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45113</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45114</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45114</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45114</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45118</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45120</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45120</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45121</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45121</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45121</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45127</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45127</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45127</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45127</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45127</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45131</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45131</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45131</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45131</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45132</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45138</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45145</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45145</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45145</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45151</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45151</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45152</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45152</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45154</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45156</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45158</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45160</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45160</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45160</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45160</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>45161</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45161</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45161</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45165</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45166</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45166</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45167</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45167</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45167</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45169</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45169</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45169</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45169</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45169</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45170</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45176</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45180</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45181</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45181</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45181</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45183</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45184</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45184</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45186</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45187</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45190</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45194</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45194</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45195</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45195</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>45195</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45196</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45197</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45197</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45198</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45198</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45198</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45198</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45198</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>45198</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45199</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45200</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45201</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45201</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45201</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45202</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45203</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45203</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45203</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45203</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45204</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45208</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45209</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43956,7 +43956,7 @@
         <v>45215</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45216</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45216</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45217</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45218</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45219</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45219</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>45223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45226</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>45228</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>45228</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45229</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45229</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45230</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45230</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45230</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>45231</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45231</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45232</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>45232</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45235</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45236</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45238</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45238</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45238</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45238</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45240</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45240</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45240</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45240</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45243</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45243</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45244</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45244</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45244</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45245</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45245</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45245</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45246</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45246</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45246</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45246</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45247</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45247</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45250</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45250</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45251</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45251</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45252</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45252</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45252</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45252</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45252</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45252</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45252</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45253</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45253</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45254</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45254</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45254</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45255</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45256</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45256</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45257</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45257</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45257</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45258</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45258</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45258</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45258</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>45258</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45258</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48784,7 +48784,7 @@
         <v>45258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45258</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>45258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>45259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45260</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>45260</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45260</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45260</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         <v>45261</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45261</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45261</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45261</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45261</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45261</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45264</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45265</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45265</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>45265</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45267</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45267</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45270</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45272</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45272</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45273</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45273</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45274</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45275</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45275</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45279</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45280</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45280</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45280</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45281</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45281</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45282</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45283</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45293</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45293</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45294</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45298</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45299</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45299</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45301</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45302</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45302</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45303</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45303</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45303</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45303</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45303</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45304</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45306</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>45307</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>45307</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45307</v>
       </c>
       <c r="C889" s="1" t="n">